--- a/output/roomself_excel/11071.xlsx
+++ b/output/roomself_excel/11071.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55896</v>
+        <v>225108</v>
       </c>
       <c r="D2" t="n">
-        <v>2304</v>
+        <v>5068</v>
       </c>
       <c r="E2" t="n">
-        <v>294</v>
+        <v>478</v>
       </c>
       <c r="F2" t="n">
-        <v>68</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30711</v>
+        <v>192510</v>
       </c>
       <c r="D3" t="n">
-        <v>1760</v>
+        <v>3544</v>
       </c>
       <c r="E3" t="n">
-        <v>416</v>
+        <v>469</v>
       </c>
       <c r="F3" t="n">
-        <v>124</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4">
@@ -520,7 +520,7 @@
         <v>2640</v>
       </c>
       <c r="E4" t="n">
-        <v>841</v>
+        <v>416</v>
       </c>
       <c r="F4" t="n">
         <v>307</v>
@@ -532,17 +532,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28103</v>
+        <v>86920</v>
       </c>
       <c r="D5" t="n">
-        <v>1344</v>
+        <v>2372</v>
       </c>
       <c r="E5" t="n">
-        <v>179</v>
+        <v>265</v>
       </c>
       <c r="F5" t="n">
         <v>29</v>
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>57909</v>
+        <v>89216</v>
       </c>
       <c r="D6" t="n">
-        <v>2288</v>
+        <v>2400</v>
       </c>
       <c r="E6" t="n">
-        <v>166</v>
+        <v>272</v>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>78358</v>
+        <v>80847</v>
       </c>
       <c r="D7" t="n">
-        <v>2356</v>
+        <v>2336</v>
       </c>
       <c r="E7" t="n">
-        <v>203</v>
+        <v>266</v>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -598,17 +598,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>86920</v>
+        <v>28103</v>
       </c>
       <c r="D8" t="n">
-        <v>2372</v>
+        <v>1344</v>
       </c>
       <c r="E8" t="n">
-        <v>265</v>
+        <v>179</v>
       </c>
       <c r="F8" t="n">
         <v>29</v>
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>89216</v>
+        <v>57909</v>
       </c>
       <c r="D9" t="n">
-        <v>2400</v>
+        <v>2288</v>
       </c>
       <c r="E9" t="n">
-        <v>272</v>
+        <v>166</v>
       </c>
       <c r="F9" t="n">
-        <v>97</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -642,14 +642,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21735</v>
+        <v>20048</v>
       </c>
       <c r="D10" t="n">
-        <v>1184</v>
+        <v>1164</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29240</v>
+        <v>121624</v>
       </c>
       <c r="D11" t="n">
-        <v>1368</v>
+        <v>3204</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>131796</v>
+        <v>30711</v>
       </c>
       <c r="D12" t="n">
-        <v>3100</v>
+        <v>1760</v>
       </c>
       <c r="E12" t="n">
-        <v>252</v>
+        <v>416</v>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>539242</v>
+        <v>131796</v>
       </c>
       <c r="D13" t="n">
-        <v>9732</v>
+        <v>3100</v>
       </c>
       <c r="E13" t="n">
-        <v>1326</v>
+        <v>252</v>
       </c>
       <c r="F13" t="n">
-        <v>978</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20048</v>
+        <v>55896</v>
       </c>
       <c r="D14" t="n">
-        <v>1164</v>
+        <v>2304</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,64 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>80847</v>
+        <v>78358</v>
       </c>
       <c r="D15" t="n">
-        <v>2336</v>
+        <v>2356</v>
       </c>
       <c r="E15" t="n">
-        <v>266</v>
+        <v>203</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>21735</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1184</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>29240</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1368</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/11071.xlsx
+++ b/output/roomself_excel/11071.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>5068</v>
       </c>
-      <c r="E2" t="n">
-        <v>478</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>137</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>414</v>
+      </c>
+      <c r="J2" t="n">
+        <v>30</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,31 @@
       <c r="D3" t="n">
         <v>3544</v>
       </c>
-      <c r="E3" t="n">
-        <v>469</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>425</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="G3" t="n">
+        <v>34</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>435</v>
+      </c>
+      <c r="J3" t="n">
+        <v>32</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +592,23 @@
       <c r="D4" t="n">
         <v>2640</v>
       </c>
-      <c r="E4" t="n">
-        <v>416</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
         <v>307</v>
       </c>
+      <c r="G4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +625,23 @@
       <c r="D5" t="n">
         <v>2372</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>265</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>29</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +658,23 @@
       <c r="D6" t="n">
         <v>2400</v>
       </c>
-      <c r="E6" t="n">
-        <v>272</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>97</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="G6" t="n">
+        <v>29</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +691,23 @@
       <c r="D7" t="n">
         <v>2336</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>266</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>35</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +724,23 @@
       <c r="D8" t="n">
         <v>1344</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>179</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>29</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +757,23 @@
       <c r="D9" t="n">
         <v>2288</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>166</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>29</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +790,15 @@
       <c r="D10" t="n">
         <v>1164</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +815,23 @@
       <c r="D11" t="n">
         <v>3204</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>201</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>35</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +848,38 @@
       <c r="D12" t="n">
         <v>1760</v>
       </c>
-      <c r="E12" t="n">
-        <v>416</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>124</v>
+        <v>87</v>
+      </c>
+      <c r="G12" t="n">
+        <v>29</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>353</v>
+      </c>
+      <c r="J12" t="n">
+        <v>37</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>87</v>
+      </c>
+      <c r="M12" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +897,31 @@
       <c r="D13" t="n">
         <v>3100</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>523</v>
+      </c>
+      <c r="G13" t="n">
+        <v>17</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>252</v>
       </c>
-      <c r="F13" t="n">
+      <c r="J13" t="n">
         <v>26</v>
       </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,11 +938,38 @@
       <c r="D14" t="n">
         <v>2304</v>
       </c>
-      <c r="E14" t="n">
-        <v>294</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>68</v>
+        <v>252</v>
+      </c>
+      <c r="G14" t="n">
+        <v>21</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>47</v>
+      </c>
+      <c r="J14" t="n">
+        <v>42</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>324</v>
+      </c>
+      <c r="M14" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -761,12 +987,23 @@
       <c r="D15" t="n">
         <v>2356</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>203</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>29</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1020,15 @@
       <c r="D16" t="n">
         <v>1184</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1045,15 @@
       <c r="D17" t="n">
         <v>1368</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/11071.xlsx
+++ b/output/roomself_excel/11071.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,66 @@
           <t>ExtWallWidth_3</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -535,6 +595,42 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>32</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>247</v>
+      </c>
+      <c r="U2" t="n">
+        <v>30</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -576,6 +672,54 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>34</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>116</v>
+      </c>
+      <c r="U3" t="n">
+        <v>34</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>347</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -609,6 +753,30 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>143</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>29</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -642,6 +810,30 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>143</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>29</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -675,6 +867,30 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>29</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -708,6 +924,30 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>35</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -741,6 +981,30 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>29</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -774,6 +1038,30 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>29</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -799,6 +1087,18 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -832,6 +1132,42 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>35</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>84</v>
+      </c>
+      <c r="U11" t="n">
+        <v>35</v>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -881,6 +1217,18 @@
       <c r="M12" t="n">
         <v>34</v>
       </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -922,6 +1270,30 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>215</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>26</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -971,6 +1343,18 @@
       <c r="M14" t="n">
         <v>17</v>
       </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1004,6 +1388,42 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>29</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>83</v>
+      </c>
+      <c r="U15" t="n">
+        <v>29</v>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1029,6 +1449,18 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1054,6 +1486,18 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
